--- a/data/trans_orig/IQ23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según del número de horas que duerme</t>
+          <t>Menores según del número de horas que duerme (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9,59; 10,02</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9,63; 10,23</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9,41; 10,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8,96; 9,28</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,56; 10,13</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,46; 10,11</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,62; 10,24</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8,9; 9,28</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9,63; 9,98</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>9,59; 10,04</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,61; 10,21</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 9,99</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8,96; 9,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9,54; 10,13</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 10,07</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 10,25</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,92; 9,27</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9,64; 10,0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 10,04</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,04</t>
+          <t>9,62; 10,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 9,23</t>
+          <t>8,97; 9,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,2</t>
+          <t>9,63; 10,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 10,46</t>
+          <t>9,84; 10,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 9,96</t>
+          <t>9,44; 9,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,3</t>
+          <t>8,9; 9,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,18</t>
+          <t>9,61; 10,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 10,12</t>
+          <t>9,55; 10,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 9,77</t>
+          <t>9,34; 9,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,27</t>
+          <t>8,91; 9,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,1</t>
+          <t>9,7; 10,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 10,17</t>
+          <t>9,76; 10,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,78</t>
+          <t>9,47; 9,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,22</t>
+          <t>8,97; 9,22</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,92</t>
+          <t>9,25; 9,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,04</t>
+          <t>9,42; 10,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 9,87</t>
+          <t>9,31; 9,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,88; 9,49</t>
+          <t>8,89; 9,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 9,62</t>
+          <t>9,2; 9,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,21</t>
+          <t>9,6; 10,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,79</t>
+          <t>9,27; 9,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 9,18</t>
+          <t>8,79; 9,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,63</t>
+          <t>9,29; 9,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 10,03</t>
+          <t>9,58; 10,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,72</t>
+          <t>9,34; 9,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,88; 9,23</t>
+          <t>8,89; 9,23</t>
         </is>
       </c>
     </row>
@@ -1141,32 +1141,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,96</t>
+          <t>9,58; 9,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,82</t>
+          <t>9,49; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,3</t>
+          <t>9,05; 9,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,77</t>
+          <t>9,41; 9,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,13</t>
+          <t>9,69; 10,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 9,55</t>
+          <t>9,23; 9,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,67</t>
+          <t>9,42; 9,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 9,97</t>
+          <t>9,69; 9,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 9,63</t>
+          <t>9,41; 9,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,23</t>
+          <t>9,02; 9,22</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,81</t>
+          <t>9,32; 9,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,53; 10,04</t>
+          <t>9,56; 10,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 9,71</t>
+          <t>9,3; 9,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,35</t>
+          <t>8,96; 9,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,89</t>
+          <t>9,45; 9,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 10,03</t>
+          <t>9,5; 10,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,67</t>
+          <t>9,23; 9,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,38</t>
+          <t>9,0; 9,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 9,95</t>
+          <t>9,59; 9,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,59</t>
+          <t>9,31; 9,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,3</t>
+          <t>9,04; 9,31</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,71</t>
+          <t>9,16; 9,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 10,15</t>
+          <t>9,25; 10,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,86</t>
+          <t>9,26; 9,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,97</t>
+          <t>9,32; 9,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,29</t>
+          <t>9,6; 10,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,83</t>
+          <t>9,19; 9,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,79; 9,16</t>
+          <t>8,76; 9,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,73</t>
+          <t>9,31; 9,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,08</t>
+          <t>9,52; 10,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,7</t>
+          <t>9,27; 9,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,18</t>
+          <t>8,9; 9,19</t>
         </is>
       </c>
     </row>
@@ -1556,19 +1556,19 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9,51; 9,71</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9,69; 9,92</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 9,93</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,7</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>9,07; 9,21</t>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,74</t>
+          <t>9,54; 9,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,16</t>
+          <t>9,0; 9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,9</t>
+          <t>9,73; 9,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,63</t>
+          <t>9,49; 9,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,16</t>
+          <t>9,04; 9,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Clase-trans_orig.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 10,02</t>
+          <t>9,57; 10,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 10,23</t>
+          <t>9,6; 10,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,41; 10,0</t>
+          <t>9,42; 10,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,13</t>
+          <t>9,56; 10,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 10,11</t>
+          <t>9,43; 10,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,24</t>
+          <t>9,61; 10,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,28</t>
+          <t>8,93; 9,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 9,98</t>
+          <t>9,64; 9,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>9,61; 10,07</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>9,59; 10,04</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 10,06</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 9,23</t>
+          <t>8,98; 9,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 10,22</t>
+          <t>9,62; 10,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 10,49</t>
+          <t>9,84; 10,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,93</t>
+          <t>9,46; 9,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,27</t>
+          <t>8,93; 9,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,15</t>
+          <t>9,6; 10,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 10,09</t>
+          <t>9,58; 10,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,8</t>
+          <t>9,34; 9,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,26</t>
+          <t>8,91; 9,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 10,1</t>
+          <t>9,69; 10,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 10,16</t>
+          <t>9,76; 10,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 9,79</t>
+          <t>9,45; 9,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 9,22</t>
+          <t>8,96; 9,22</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,89</t>
+          <t>9,24; 9,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 10,03</t>
+          <t>9,41; 10,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,89</t>
+          <t>9,26; 9,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,47</t>
+          <t>8,89; 9,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 9,62</t>
+          <t>9,21; 9,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 10,2</t>
+          <t>9,57; 10,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,75</t>
+          <t>9,25; 9,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 9,2</t>
+          <t>8,77; 9,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,67</t>
+          <t>9,28; 9,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,03</t>
+          <t>9,61; 10,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,74</t>
+          <t>9,33; 9,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,23</t>
+          <t>8,89; 9,22</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,7</t>
+          <t>9,34; 9,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,58; 9,97</t>
+          <t>9,56; 9,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,83</t>
+          <t>9,49; 9,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,3</t>
+          <t>9,03; 9,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,78</t>
+          <t>9,42; 9,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,15</t>
+          <t>9,7; 10,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,57</t>
+          <t>9,23; 9,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,88; 9,22</t>
+          <t>8,9; 9,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 9,68</t>
+          <t>9,44; 9,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,99</t>
+          <t>9,7; 10,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 9,22</t>
+          <t>9,01; 9,22</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1276,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,78</t>
+          <t>9,31; 9,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,06</t>
+          <t>9,54; 10,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,71</t>
+          <t>9,3; 9,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,34</t>
+          <t>8,97; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,92</t>
+          <t>9,44; 9,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,5; 10,03</t>
+          <t>9,49; 10,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,65</t>
+          <t>9,24; 9,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,4</t>
+          <t>8,99; 9,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,45; 9,76</t>
+          <t>9,43; 9,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,31</t>
+          <t>9,03; 9,3</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,16; 9,75</t>
+          <t>9,15; 9,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 10,12</t>
+          <t>9,3; 10,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,92; 9,35</t>
+          <t>8,93; 9,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 9,91</t>
+          <t>9,33; 9,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,6; 10,29</t>
+          <t>9,56; 10,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,19; 9,83</t>
+          <t>9,18; 9,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 9,12</t>
+          <t>8,76; 9,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,52; 10,09</t>
+          <t>9,52; 10,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 9,72</t>
+          <t>9,29; 9,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 9,71</t>
+          <t>9,51; 9,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,69; 9,92</t>
+          <t>9,7; 9,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1576,32 +1576,32 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 9,73</t>
+          <t>9,55; 9,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72; 9,95</t>
+          <t>9,72; 9,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,61</t>
+          <t>9,41; 9,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,0; 9,17</t>
+          <t>9,01; 9,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 9,69</t>
+          <t>9,56; 9,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 9,89</t>
+          <t>9,74; 9,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,04; 9,16</t>
+          <t>9,05; 9,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ23-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,62 +648,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,73</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,89</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9,7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9,08</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9,81</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>9,81</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>9,81</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>9,1</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 10,02</t>
+          <t>9,54; 10,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 10,21</t>
+          <t>9,43; 10,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 10,01</t>
+          <t>9,64; 10,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,28</t>
+          <t>8,97; 9,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,14</t>
+          <t>9,59; 10,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 10,07</t>
+          <t>9,61; 10,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,21</t>
+          <t>9,43; 9,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,28</t>
+          <t>8,93; 9,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 9,99</t>
+          <t>9,64; 10,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,07</t>
+          <t>9,62; 10,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 10,04</t>
+          <t>9,62; 10,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 9,23</t>
+          <t>8,99; 9,2</t>
         </is>
       </c>
     </row>
@@ -788,39 +788,39 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,86</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,8</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,53</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,1</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,68</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9,08</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>9,07</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 10,23</t>
+          <t>9,61; 10,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 10,46</t>
+          <t>9,55; 10,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 9,93</t>
+          <t>9,35; 9,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,3</t>
+          <t>8,89; 9,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,6; 10,16</t>
+          <t>9,62; 10,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 10,12</t>
+          <t>9,82; 10,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,78</t>
+          <t>9,48; 9,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 9,27</t>
+          <t>8,9; 9,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 10,08</t>
+          <t>9,69; 10,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 10,19</t>
+          <t>9,76; 10,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 9,22</t>
+          <t>8,94; 9,2</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,88</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,5</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,96</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,54</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,88</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,5</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>9,01</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,87</t>
+          <t>9,21; 9,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,41; 10,02</t>
+          <t>9,58; 10,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,84</t>
+          <t>9,27; 9,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,48</t>
+          <t>8,76; 9,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,21; 9,63</t>
+          <t>9,26; 9,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,57; 10,21</t>
+          <t>9,45; 10,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,77</t>
+          <t>9,28; 9,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 9,18</t>
+          <t>8,84; 9,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 9,64</t>
+          <t>9,27; 9,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 10,04</t>
+          <t>9,57; 10,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 9,22</t>
+          <t>8,85; 9,19</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,89</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,38</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,03</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,76</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,65</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,17</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,58</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,89</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,38</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,06</t>
+          <t>9,14</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>9,08</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,68</t>
+          <t>9,42; 9,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>9,69; 10,13</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9,22; 9,55</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8,86; 9,2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,36; 9,7</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>9,56; 9,96</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,49; 9,84</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,03; 9,3</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 9,78</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 10,15</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 9,55</t>
+          <t>9,49; 9,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,22</t>
+          <t>9,01; 9,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,68</t>
+          <t>9,43; 9,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 10,0</t>
+          <t>9,71; 9,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 9,65</t>
+          <t>9,4; 9,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,22</t>
+          <t>8,96; 9,19</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,73</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,43</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,14</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,55</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,77</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,48</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,15</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,73</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,17</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,14</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,8</t>
+          <t>9,42; 9,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 10,06</t>
+          <t>9,52; 10,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 9,72</t>
+          <t>9,26; 9,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 9,33</t>
+          <t>8,98; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,44; 9,9</t>
+          <t>9,32; 9,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 10,03</t>
+          <t>9,53; 10,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,65</t>
+          <t>9,28; 9,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 9,38</t>
+          <t>8,99; 9,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,43; 9,76</t>
+          <t>9,45; 9,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,59; 9,94</t>
+          <t>9,59; 9,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,6</t>
+          <t>9,3; 9,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 9,3</t>
+          <t>9,02; 9,27</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9,86</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,44</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8,93</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9,41</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9,64</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>9,52</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,13</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,86</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,96</t>
+          <t>9,1</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>9,02</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 9,74</t>
+          <t>9,33; 9,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,3; 10,08</t>
+          <t>9,56; 10,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 9,83</t>
+          <t>9,16; 9,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,93; 9,36</t>
+          <t>8,76; 9,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,98</t>
+          <t>9,16; 9,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 10,22</t>
+          <t>9,29; 10,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 9,81</t>
+          <t>9,25; 9,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 9,14</t>
+          <t>8,9; 9,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,31; 9,74</t>
+          <t>9,34; 9,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,52; 10,05</t>
+          <t>9,54; 10,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 9,73</t>
+          <t>9,29; 9,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,9; 9,19</t>
+          <t>8,89; 9,16</t>
         </is>
       </c>
     </row>
@@ -1488,62 +1488,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>9,6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,81</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>9,61</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9,11</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>9,82</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,51</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9,56</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,08</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,11</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9,54; 9,74</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9,72; 9,95</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9,41; 9,61</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8,98; 9,13</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9,7; 9,93</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9,51; 9,7</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 9,21</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>9,55; 9,73</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,72; 9,94</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,41; 9,6</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,01; 9,17</t>
+          <t>9,04; 9,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,56; 9,69</t>
+          <t>9,55; 9,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 9,9</t>
+          <t>9,73; 9,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,49; 9,62</t>
+          <t>9,49; 9,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,16</t>
+          <t>9,03; 9,14</t>
         </is>
       </c>
     </row>
